--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/StructureDefinition/CoreLocalizacionCl</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/CoreLocalizacionCl</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1179,7 +1179,7 @@
     <t>Códigos Comuna, Ministerio del Interior, 2018</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/VSCodigosComunaCL</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosComunaCL</t>
   </si>
   <si>
     <t>Address.city</t>
@@ -1210,7 +1210,7 @@
     <t>Códigos Provincia, Ministerio del Interior, 2018</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/VSCodigosProvinciasCL</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosProvinciasCL</t>
   </si>
   <si>
     <t>Address.district</t>
@@ -1235,7 +1235,7 @@
     <t>Códigos Regiones, Ministerio del Interior, 2018</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/VSCodigosRegionesCL</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigosRegionesCL</t>
   </si>
   <si>
     <t>Address.state</t>
@@ -1275,7 +1275,7 @@
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/CodPais</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/CodPais</t>
   </si>
   <si>
     <t>Address.country</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>77</v>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-LocationLE.xlsx
+++ b/refs/heads/main/StructureDefinition-LocationLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
